--- a/tools/excel/scf/scf-2026.3.xlsx
+++ b/tools/excel/scf/scf-2026.3.xlsx
@@ -22,7 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -52,8 +54,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -549,10 +552,8 @@
           <t>publication_date</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
+      <c r="B11" s="1" t="n">
+        <v>46286</v>
       </c>
     </row>
   </sheetData>
@@ -566,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,6 +684,18 @@
       <c r="B10" t="inlineStr">
         <is>
           <t>scores</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>field_visibility</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>{"score": {"auditor": "edit", "respondent": "hidden"}, "is_scored": {"auditor": "edit", "respondent": "hidden"}, "documentation_score": {"auditor": "hidden", "respondent": "hidden"}, "result": {"auditor": "edit", "respondent": "edit"}, "extended_result": {"auditor": "hidden", "respondent": "hidden"}, "status": {"auditor": "hidden", "respondent": "hidden"}, "task_templates": {"auditor": "hidden", "respondent": "hidden"}, "applied_controls": {"auditor": "edit", "respondent": "edit"}}</t>
         </is>
       </c>
     </row>
@@ -58739,6 +58752,11 @@
           <t>Not Performed</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>This level of maturity is defined as “non-existence practices,” where the control is not being performed. Practices are non-existent, where a reasonable person would conclude the control is not being performed.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -58749,6 +58767,11 @@
           <t>Performed Informally</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>This level of maturity is defined as “ad hoc practices,” where the control is being performed, but lacks completeness &amp; consistency. Performance depends on specific knowledge and effort of the individual performing the task(s), where the performance of these practices is not proactively governed.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -58757,6 +58780,11 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>Planned &amp; Tracked</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Practices are “requirements-driven” where the intent of control is met in some circumstances, but not standardized across the entire organization. Controls are implemented in some, but not all applicable circumstances/environments (e.g., specific enclaves, facilities or locations).</t>
         </is>
       </c>
     </row>
@@ -58769,6 +58797,11 @@
           <t>Well Defined</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>This level of maturity is defined as “enterprise-wide standardization,” where the practices are well-defined and standardized across the organization. Controls are implemented in all applicable circumstances/environments (deviations are documented and justified).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -58779,6 +58812,11 @@
           <t>Quantitatively Controlled</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>This level of maturity is defined as “metrics-driven practices,” where in addition to being well-defined and standardized practices across the organization, there are detailed metrics to enable governance oversight.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -58787,6 +58825,11 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>Continuously Improving</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>This level of maturity is defined as “world-class practices,” where the practices are not only well-defined and standardized across the organization, as well as having detailed metrics, but the process is continuously improving.</t>
         </is>
       </c>
     </row>
